--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB JOVENS ALMÀSSERA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB JOVENS ALMÀSSERA.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>37.8146</v>
+        <v>30.8389</v>
       </c>
       <c r="E2" t="n">
-        <v>34.856</v>
+        <v>27.1797</v>
       </c>
       <c r="F2" t="n">
-        <v>2.959000000000001</v>
+        <v>3.659400000000001</v>
       </c>
       <c r="G2" t="n">
         <v>22.4715</v>
@@ -610,13 +610,13 @@
         <v>42.5155</v>
       </c>
       <c r="S2" t="n">
-        <v>11.4498</v>
+        <v>4.474399999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>11.7502</v>
+        <v>4.0743</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3</v>
+        <v>0.4004</v>
       </c>
       <c r="V2" t="n">
         <v>0.4110999999999999</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>35.1963</v>
+        <v>27.0678</v>
       </c>
       <c r="E3" t="n">
-        <v>26.7997</v>
+        <v>22.0908</v>
       </c>
       <c r="F3" t="n">
-        <v>8.396100000000001</v>
+        <v>4.9772</v>
       </c>
       <c r="G3" t="n">
         <v>20.622</v>
@@ -688,13 +688,13 @@
         <v>59.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>8.504100000000001</v>
+        <v>0.3755999999999997</v>
       </c>
       <c r="T3" t="n">
-        <v>4.4057</v>
+        <v>-0.3037000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>4.098400000000001</v>
+        <v>0.6789000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>20.9138</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>29.5803</v>
+        <v>25.9829</v>
       </c>
       <c r="E4" t="n">
-        <v>17.0471</v>
+        <v>13.6424</v>
       </c>
       <c r="F4" t="n">
-        <v>12.5329</v>
+        <v>12.3404</v>
       </c>
       <c r="G4" t="n">
         <v>22.2827</v>
@@ -766,13 +766,13 @@
         <v>44.5315</v>
       </c>
       <c r="S4" t="n">
-        <v>6.805000000000001</v>
+        <v>3.2075</v>
       </c>
       <c r="T4" t="n">
-        <v>6.257000000000001</v>
+        <v>2.8518</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5481000000000001</v>
+        <v>0.3556</v>
       </c>
       <c r="V4" t="n">
         <v>-9.036899999999999</v>
@@ -799,13 +799,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>14.1234</v>
+        <v>15.2586</v>
       </c>
       <c r="E5" t="n">
-        <v>16.2576</v>
+        <v>16.6567</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.133900000000001</v>
+        <v>-1.398000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>-13.0619</v>
@@ -844,13 +844,13 @@
         <v>27.4888</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8619999999999997</v>
+        <v>0.2732</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2603999999999999</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1223</v>
+        <v>-0.3865</v>
       </c>
       <c r="V5" t="n">
         <v>13.2034</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>9.8522</v>
+        <v>10.8537</v>
       </c>
       <c r="E6" t="n">
-        <v>9.8522</v>
+        <v>5.549200000000002</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5.3043</v>
       </c>
       <c r="G6" t="n">
-        <v>9.8522</v>
+        <v>-3.138100000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2263</v>
+        <v>-1.8803</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6259</v>
+        <v>-1.2581</v>
       </c>
       <c r="J6" t="n">
-        <v>9.8522</v>
+        <v>16.6951</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2263</v>
+        <v>12.6257</v>
       </c>
       <c r="L6" t="n">
-        <v>5.6259</v>
+        <v>4.069400000000002</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-19.8334</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-14.5058</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-5.3278</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.8643</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-33.9026</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>39.7668</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-4.9701</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-2.2815</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-2.6881</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>13.0976</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>25.0384</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-11.941</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ROSELLO ORTS</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>7.987500000000001</v>
+        <v>9.8522</v>
       </c>
       <c r="E7" t="n">
-        <v>7.6295</v>
+        <v>9.8522</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3578999999999999</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6095999999999995</v>
+        <v>9.8522</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2298</v>
+        <v>4.2263</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6202</v>
+        <v>5.6259</v>
       </c>
       <c r="J7" t="n">
-        <v>6.794</v>
+        <v>9.8522</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4249</v>
+        <v>4.2263</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3688999999999999</v>
+        <v>5.6259</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.1843</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.1951</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9893</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.2307</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-10.0793</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>16.3097</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>6.705100000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>6.7816</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07599999999999993</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.5581</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1332</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.6915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. ROIG VALERO</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>1.274699999999999</v>
+        <v>4.632200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5947000000000003</v>
+        <v>3.928999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6802000000000001</v>
+        <v>0.7032000000000009</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9540000000000004</v>
+        <v>3.688900000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4531</v>
+        <v>4.215900000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4073</v>
+        <v>-0.5271999999999997</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3264</v>
+        <v>24.76</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3027999999999998</v>
+        <v>22.7486</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0237</v>
+        <v>2.0115</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2807</v>
+        <v>-21.0714</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1503</v>
+        <v>-18.5325</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.431</v>
+        <v>-2.5386</v>
       </c>
       <c r="P8" t="n">
-        <v>5.680899999999999</v>
+        <v>2.382099999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-43.2489</v>
       </c>
       <c r="R8" t="n">
-        <v>7.5135</v>
+        <v>45.6309</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.6711</v>
+        <v>-1.4181</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4539</v>
+        <v>-1.4055</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2171</v>
+        <v>-0.01230000000000014</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7811000000000001</v>
+        <v>-0.0207</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5547</v>
+        <v>23.8235</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.3357</v>
+        <v>-23.8443</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>O. ROIG VALERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3907000000000007</v>
+        <v>3.346099999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.919899999999999</v>
+        <v>1.9549</v>
       </c>
       <c r="F9" t="n">
-        <v>5.310300000000001</v>
+        <v>1.3911</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.138100000000001</v>
+        <v>-0.9540000000000004</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8803</v>
+        <v>1.4531</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2581</v>
+        <v>-2.4073</v>
       </c>
       <c r="J9" t="n">
-        <v>16.6951</v>
+        <v>1.3264</v>
       </c>
       <c r="K9" t="n">
-        <v>12.6257</v>
+        <v>0.3027999999999998</v>
       </c>
       <c r="L9" t="n">
-        <v>4.069400000000002</v>
+        <v>1.0237</v>
       </c>
       <c r="M9" t="n">
-        <v>-19.8334</v>
+        <v>-2.2807</v>
       </c>
       <c r="N9" t="n">
-        <v>-14.5058</v>
+        <v>1.1503</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.3278</v>
+        <v>-3.431</v>
       </c>
       <c r="P9" t="n">
-        <v>5.8643</v>
+        <v>5.680899999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-33.9026</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>39.7668</v>
+        <v>7.5135</v>
       </c>
       <c r="S9" t="n">
-        <v>-15.4329</v>
+        <v>-0.5998999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-12.7508</v>
+        <v>-0.09380000000000002</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.6821</v>
+        <v>-0.5061</v>
       </c>
       <c r="V9" t="n">
-        <v>13.0976</v>
+        <v>-0.7811000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>25.0384</v>
+        <v>2.5547</v>
       </c>
       <c r="X9" t="n">
-        <v>-11.941</v>
+        <v>-3.3357</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>P. ROSELLO ORTS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4698000000000003</v>
+        <v>2.9298</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0011</v>
+        <v>2.8359</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4705</v>
+        <v>0.09390000000000021</v>
       </c>
       <c r="G10" t="n">
-        <v>3.688900000000001</v>
+        <v>0.6095999999999995</v>
       </c>
       <c r="H10" t="n">
-        <v>4.215900000000001</v>
+        <v>2.2298</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5271999999999997</v>
+        <v>-1.6202</v>
       </c>
       <c r="J10" t="n">
-        <v>24.76</v>
+        <v>6.794</v>
       </c>
       <c r="K10" t="n">
-        <v>22.7486</v>
+        <v>6.4249</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0115</v>
+        <v>0.3688999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-21.0714</v>
+        <v>-6.1843</v>
       </c>
       <c r="N10" t="n">
-        <v>-18.5325</v>
+        <v>-4.1951</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5386</v>
+        <v>-1.9893</v>
       </c>
       <c r="P10" t="n">
-        <v>2.382099999999999</v>
+        <v>6.2307</v>
       </c>
       <c r="Q10" t="n">
-        <v>-43.2489</v>
+        <v>-10.0793</v>
       </c>
       <c r="R10" t="n">
-        <v>45.6309</v>
+        <v>16.3097</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.5204</v>
+        <v>1.6477</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.3334</v>
+        <v>1.9877</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.1866</v>
+        <v>-0.3401000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0207</v>
+        <v>-5.5581</v>
       </c>
       <c r="W10" t="n">
-        <v>23.8235</v>
+        <v>4.1332</v>
       </c>
       <c r="X10" t="n">
-        <v>-23.8443</v>
+        <v>-9.6915</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RUBIO MONFORT</t>
+          <t>M. ANDRES VALVERDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4991000000000002</v>
+        <v>-0.8869</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-2.534</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07299999999999995</v>
+        <v>1.6471</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9636</v>
+        <v>1.0961</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9989</v>
+        <v>0.1154</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03539999999999999</v>
+        <v>0.9808000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2181999999999999</v>
+        <v>-0.3843</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4583999999999999</v>
+        <v>-0.4676999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6767000000000001</v>
+        <v>0.0834</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1817</v>
+        <v>1.4803</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5404</v>
+        <v>0.5829000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6413</v>
+        <v>0.8974</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9162999999999999</v>
+        <v>-0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0996</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0159</v>
+        <v>1.0996</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1194999999999999</v>
+        <v>-1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3092</v>
+        <v>-0.3172</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4288000000000001</v>
+        <v>-0.9328000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3323</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ANDRES VALVERDE</t>
+          <t>J. RUBIO MONFORT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2304</v>
+        <v>-1.1037</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8774</v>
+        <v>-1.0529</v>
       </c>
       <c r="F12" t="n">
-        <v>1.647</v>
+        <v>-0.05080000000000018</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0961</v>
+        <v>-0.9636</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1154</v>
+        <v>-0.9989</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9808000000000001</v>
+        <v>0.03539999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3843</v>
+        <v>0.2181999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4676999999999999</v>
+        <v>-0.4583999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0834</v>
+        <v>0.6767000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4803</v>
+        <v>-1.1817</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5829000000000001</v>
+        <v>-0.5404</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8974</v>
+        <v>-0.6413</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.733</v>
+        <v>0.9162999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8326</v>
+        <v>-1.0996</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0996</v>
+        <v>2.0159</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5936</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6607000000000001</v>
+        <v>-0.1715</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9329000000000001</v>
+        <v>-0.5526</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.3323</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.3323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MARTINEZ PITARCH</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9198</v>
+        <v>-1.5605</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6194</v>
+        <v>3.1489</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3005</v>
+        <v>-4.709099999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8361</v>
+        <v>-17.802</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1951</v>
+        <v>-19.5741</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.641</v>
+        <v>1.771699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6194</v>
+        <v>16.8076</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0217</v>
+        <v>2.399</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.641</v>
+        <v>14.4086</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2167</v>
+        <v>-34.6096</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2167</v>
+        <v>-21.9727</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-12.637</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1833</v>
+        <v>29.5044</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-13.3779</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1833</v>
+        <v>42.8822</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-12.1681</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-7.2599</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-4.9084</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.267</v>
+        <v>-1.0946</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>6.978899999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.267</v>
+        <v>-8.073499999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MUNOZ TABERNER</t>
+          <t>J. MARTINEZ PITARCH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3407</v>
+        <v>-1.8237</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7857</v>
+        <v>-0.5232</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5551</v>
+        <v>-1.3005</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9777</v>
+        <v>-0.8361</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6572</v>
+        <v>-0.1951</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6348</v>
+        <v>-0.641</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.217</v>
+        <v>-0.6194</v>
       </c>
       <c r="K14" t="n">
-        <v>0.065</v>
+        <v>0.0217</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2821</v>
+        <v>-0.641</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2394</v>
+        <v>-0.2167</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.2167</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3528</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5463</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3854</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1609</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>N. MUNOZ TABERNER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.2481</v>
+        <v>-2.0493</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.797700000000001</v>
+        <v>-1.5933</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.4506</v>
+        <v>-0.456</v>
       </c>
       <c r="G15" t="n">
-        <v>-17.802</v>
+        <v>-0.9777</v>
       </c>
       <c r="H15" t="n">
-        <v>-19.5741</v>
+        <v>0.6572</v>
       </c>
       <c r="I15" t="n">
-        <v>1.771699999999999</v>
+        <v>-1.6348</v>
       </c>
       <c r="J15" t="n">
-        <v>16.8076</v>
+        <v>-1.217</v>
       </c>
       <c r="K15" t="n">
-        <v>2.399</v>
+        <v>0.065</v>
       </c>
       <c r="L15" t="n">
-        <v>14.4086</v>
+        <v>-1.2821</v>
       </c>
       <c r="M15" t="n">
-        <v>-34.6096</v>
+        <v>0.2394</v>
       </c>
       <c r="N15" t="n">
-        <v>-21.9727</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.637</v>
+        <v>-0.3528</v>
       </c>
       <c r="P15" t="n">
-        <v>29.5044</v>
+        <v>0.1833</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.3779</v>
+        <v>-0.1833</v>
       </c>
       <c r="R15" t="n">
-        <v>42.8822</v>
+        <v>0.3665</v>
       </c>
       <c r="S15" t="n">
-        <v>-27.8558</v>
+        <v>-1.2549</v>
       </c>
       <c r="T15" t="n">
-        <v>-17.2062</v>
+        <v>-0.1931</v>
       </c>
       <c r="U15" t="n">
-        <v>-10.6494</v>
+        <v>-1.0618</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0946</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>6.978899999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.073499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>-17.6955</v>
+        <v>-13.6812</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.881999999999999</v>
+        <v>-1.710899999999998</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.8136</v>
+        <v>-11.9704</v>
       </c>
       <c r="G16" t="n">
         <v>-16.6485</v>
@@ -1702,13 +1702,13 @@
         <v>36.6516</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.4103</v>
+        <v>-3.396</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.8835</v>
+        <v>-1.7122</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.5271</v>
+        <v>-1.6838</v>
       </c>
       <c r="V16" t="n">
         <v>5.813499999999999</v>
@@ -1735,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-18.1758</v>
+        <v>-16.5375</v>
       </c>
       <c r="E17" t="n">
-        <v>-21.8423</v>
+        <v>-22.5969</v>
       </c>
       <c r="F17" t="n">
-        <v>3.666999999999999</v>
+        <v>6.0596</v>
       </c>
       <c r="G17" t="n">
         <v>-25.3005</v>
@@ -1780,13 +1780,13 @@
         <v>34.6357</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.4761</v>
+        <v>-2.8378</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4799</v>
+        <v>-0.2745000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.9559</v>
+        <v>-2.5633</v>
       </c>
       <c r="V17" t="n">
         <v>0.9721000000000003</v>
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-23.3638</v>
+        <v>-18.4884</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.1271</v>
+        <v>-18.6808</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.236</v>
+        <v>0.1927999999999996</v>
       </c>
       <c r="G18" t="n">
         <v>-26.8593</v>
@@ -1858,13 +1858,13 @@
         <v>36.6515</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.5827</v>
+        <v>-2.7072</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.6573</v>
+        <v>-0.2105</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.925800000000001</v>
+        <v>-2.4963</v>
       </c>
       <c r="V18" t="n">
         <v>12.1775</v>
@@ -1891,19 +1891,19 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>53.27670000000001</v>
+        <v>74.63099999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>49.6143</v>
+        <v>58.14770000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6632</v>
+        <v>16.4842</v>
       </c>
       <c r="G19" t="n">
         <v>-25.9187</v>
       </c>
       <c r="H19" t="n">
-        <v>9.830500000000015</v>
+        <v>9.830500000000008</v>
       </c>
       <c r="I19" t="n">
         <v>-35.7497</v>
@@ -1915,7 +1915,7 @@
         <v>185.9517</v>
       </c>
       <c r="L19" t="n">
-        <v>45.89900000000001</v>
+        <v>45.899</v>
       </c>
       <c r="M19" t="n">
         <v>-257.7704</v>
@@ -1936,13 +1936,13 @@
         <v>437.9849</v>
       </c>
       <c r="S19" t="n">
-        <v>-42.6067</v>
+        <v>-21.2518</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.0872</v>
+        <v>-4.553599999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-29.5184</v>
+        <v>-16.6972</v>
       </c>
       <c r="V19" t="n">
         <v>48.49830000000001</v>
